--- a/data/trans_camb/P71_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P71_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,1; 17,67</t>
+          <t>9,86; 18,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,61; 24,62</t>
+          <t>15,48; 24,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 0,94</t>
+          <t>-7,09; 0,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 11,24</t>
+          <t>1,62; 11,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,95; 15,16</t>
+          <t>6,3; 15,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,29; -4,76</t>
+          <t>-13,45; -4,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,63; 13,29</t>
+          <t>7,14; 13,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,9; 18,67</t>
+          <t>12,03; 18,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,87; -3,15</t>
+          <t>-8,8; -2,73</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>54,65; 135,03</t>
+          <t>56,47; 145,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>93,2; 193,89</t>
+          <t>92,08; 194,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-40,28; 9,16</t>
+          <t>-41,07; 7,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,14; 52,49</t>
+          <t>5,61; 49,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,18; 69,84</t>
+          <t>23,69; 73,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,37; -22,18</t>
+          <t>-51,98; -22,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,99; 74,29</t>
+          <t>33,84; 75,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>57,65; 104,83</t>
+          <t>56,92; 105,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-43,06; -17,66</t>
+          <t>-42,47; -15,24</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,53; 22,72</t>
+          <t>14,62; 22,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,39; 21,2</t>
+          <t>13,36; 21,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,85; -3,39</t>
+          <t>-12,77; -3,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,17; 13,8</t>
+          <t>4,81; 13,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,61; 13,16</t>
+          <t>4,95; 13,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,76; -8,81</t>
+          <t>-15,7; -8,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,88; 16,92</t>
+          <t>11,0; 16,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,07; 15,66</t>
+          <t>10,06; 15,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-14,18; -7,36</t>
+          <t>-14,53; -7,35</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>75,72; 149,21</t>
+          <t>77,4; 156,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,78; 139,74</t>
+          <t>69,83; 144,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-70,46; -21,86</t>
+          <t>-73,6; -23,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,13; 57,74</t>
+          <t>17,3; 56,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,88; 53,39</t>
+          <t>17,61; 55,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,79; -36,72</t>
+          <t>-55,25; -36,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,48; 83,82</t>
+          <t>47,47; 83,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>43,62; 77,8</t>
+          <t>43,83; 78,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-64,25; -35,81</t>
+          <t>-66,12; -36,63</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,89; 20,54</t>
+          <t>10,65; 20,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,99; 27,72</t>
+          <t>17,6; 27,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,17; -1,42</t>
+          <t>-10,13; -1,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 11,46</t>
+          <t>1,41; 11,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,41; 21,75</t>
+          <t>10,83; 20,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,95; -11,78</t>
+          <t>-26,32; -11,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,5; 14,32</t>
+          <t>7,14; 14,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,12; 23,05</t>
+          <t>16,06; 23,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-16,84; -8,32</t>
+          <t>-18,28; -8,53</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>49,98; 119,7</t>
+          <t>47,47; 117,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>80,54; 159,95</t>
+          <t>77,4; 159,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-46,59; -7,72</t>
+          <t>-47,5; -7,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,25; 41,05</t>
+          <t>4,23; 39,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>34,57; 79,46</t>
+          <t>32,67; 74,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-80,31; -40,22</t>
+          <t>-79,47; -40,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,08; 61,28</t>
+          <t>26,74; 62,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>58,69; 99,01</t>
+          <t>60,25; 100,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-66,95; -35,16</t>
+          <t>-69,96; -35,56</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 6,52</t>
+          <t>-1,12; 6,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 7,67</t>
+          <t>0,06; 7,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,57; -2,16</t>
+          <t>-9,83; -2,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,3; -0,93</t>
+          <t>-8,99; -1,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 2,88</t>
+          <t>-5,18; 3,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 9,24</t>
+          <t>-13,52; 9,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 1,32</t>
+          <t>-4,23; 1,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 4,14</t>
+          <t>-1,52; 3,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 3,27</t>
+          <t>-10,54; 3,27</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 34,95</t>
+          <t>-4,99; 34,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 41,45</t>
+          <t>0,25; 39,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,56; -11,06</t>
+          <t>-42,7; -14,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-29,36; -3,71</t>
+          <t>-28,63; -5,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 10,23</t>
+          <t>-16,36; 11,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-45,0; 32,56</t>
+          <t>-44,34; 32,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 5,46</t>
+          <t>-16,0; 4,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 17,38</t>
+          <t>-5,74; 15,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-39,65; 15,05</t>
+          <t>-39,91; 14,58</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,51; 14,59</t>
+          <t>10,64; 14,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13,3; 17,53</t>
+          <t>13,32; 17,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,92; -4,04</t>
+          <t>-9,08; -3,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,09</t>
+          <t>1,56; 6,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,86; 10,37</t>
+          <t>5,45; 10,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,21; -5,86</t>
+          <t>-14,3; -5,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,42; 9,65</t>
+          <t>6,5; 9,7</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,91; 13,22</t>
+          <t>10,18; 13,31</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-10,67; -5,45</t>
+          <t>-10,79; -5,63</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>54,41; 84,54</t>
+          <t>55,83; 85,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>69,88; 103,67</t>
+          <t>70,34; 103,99</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-47,77; -23,5</t>
+          <t>-49,51; -23,2</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5,04; 22,74</t>
+          <t>5,5; 22,88</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>20,02; 38,58</t>
+          <t>18,72; 38,62</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-49,98; -21,82</t>
+          <t>-50,14; -21,34</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,03; 43,52</t>
+          <t>27,29; 43,99</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>41,19; 59,59</t>
+          <t>42,53; 60,45</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-44,86; -23,19</t>
+          <t>-45,3; -24,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P71_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P71_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,87</t>
+          <t>-1,43</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-8,8</t>
+          <t>-6,91</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-5,69</t>
+          <t>-4,08</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,86; 18,31</t>
+          <t>9,7; 18,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,48; 24,73</t>
+          <t>15,6; 24,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 0,83</t>
+          <t>-5,31; 2,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 11,04</t>
+          <t>1,55; 10,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,3; 15,84</t>
+          <t>5,6; 15,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,45; -4,91</t>
+          <t>-10,89; -2,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,14; 13,34</t>
+          <t>6,82; 13,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,03; 18,78</t>
+          <t>12,17; 18,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,8; -2,73</t>
+          <t>-6,99; -1,26</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-19,65%</t>
+          <t>-9,78%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-36,65%</t>
+          <t>-28,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-29,49%</t>
+          <t>-21,14%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>56,47; 145,65</t>
+          <t>57,52; 145,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>92,08; 194,52</t>
+          <t>91,3; 195,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-41,07; 7,71</t>
+          <t>-32,07; 19,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,61; 49,53</t>
+          <t>6,24; 48,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,69; 73,73</t>
+          <t>21,0; 69,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,98; -22,66</t>
+          <t>-41,77; -12,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,84; 75,74</t>
+          <t>31,84; 74,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>56,92; 105,44</t>
+          <t>57,8; 105,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-42,47; -15,24</t>
+          <t>-33,51; -7,79</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-7,39</t>
+          <t>-3,5</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-12,25</t>
+          <t>-11,75</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-10,08</t>
+          <t>-7,63</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,62; 22,67</t>
+          <t>14,64; 22,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,36; 21,3</t>
+          <t>13,47; 21,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,77; -3,57</t>
+          <t>-7,14; -0,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,81; 13,37</t>
+          <t>4,65; 13,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 13,1</t>
+          <t>4,56; 12,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,7; -8,99</t>
+          <t>-15,22; -8,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,0; 16,83</t>
+          <t>10,92; 16,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,06; 15,86</t>
+          <t>10,14; 15,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-14,53; -7,35</t>
+          <t>-9,98; -5,11</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-44,11%</t>
+          <t>-20,92%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-46,61%</t>
+          <t>-44,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-46,83%</t>
+          <t>-35,44%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>77,4; 156,84</t>
+          <t>78,82; 148,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,83; 144,36</t>
+          <t>74,08; 145,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-73,6; -23,71</t>
+          <t>-37,97; -0,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,3; 56,18</t>
+          <t>16,03; 55,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,61; 55,36</t>
+          <t>15,84; 53,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,25; -36,29</t>
+          <t>-53,81; -34,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,47; 83,08</t>
+          <t>46,71; 83,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>43,83; 78,94</t>
+          <t>43,7; 78,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-66,12; -36,63</t>
+          <t>-43,82; -25,59</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-6,11</t>
+          <t>-5,71</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-17,42</t>
+          <t>-13,16</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-11,78</t>
+          <t>-9,41</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,65; 20,27</t>
+          <t>10,74; 20,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,6; 27,55</t>
+          <t>17,89; 27,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,13; -1,53</t>
+          <t>-9,95; -1,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 11,07</t>
+          <t>0,95; 11,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,83; 20,82</t>
+          <t>10,79; 21,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,32; -11,89</t>
+          <t>-17,53; -8,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,14; 14,59</t>
+          <t>7,55; 14,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,06; 23,17</t>
+          <t>15,92; 23,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,28; -8,53</t>
+          <t>-12,54; -6,22</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-31,09%</t>
+          <t>-29,07%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-57,08%</t>
+          <t>-43,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-46,98%</t>
+          <t>-37,55%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47,47; 117,43</t>
+          <t>49,49; 119,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>77,4; 159,32</t>
+          <t>81,01; 161,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-47,5; -7,7</t>
+          <t>-45,73; -8,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,23; 39,88</t>
+          <t>2,31; 38,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32,67; 74,3</t>
+          <t>31,38; 76,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-79,47; -40,3</t>
+          <t>-52,74; -31,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,74; 62,12</t>
+          <t>28,04; 60,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>60,25; 100,99</t>
+          <t>59,55; 99,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-69,96; -35,56</t>
+          <t>-46,75; -26,82</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-5,99</t>
+          <t>-4,3</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-7,13</t>
+          <t>-11,44</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-6,44</t>
+          <t>-8,02</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 6,33</t>
+          <t>-1,24; 6,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 7,73</t>
+          <t>-0,39; 7,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,83; -2,81</t>
+          <t>-8,17; -0,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,99; -1,49</t>
+          <t>-9,01; -1,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 3,12</t>
+          <t>-5,24; 2,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 9,12</t>
+          <t>-15,09; -7,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 1,13</t>
+          <t>-4,62; 1,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 3,74</t>
+          <t>-1,9; 4,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 3,27</t>
+          <t>-10,59; -5,44</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-28,67%</t>
+          <t>-20,6%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-23,73%</t>
+          <t>-38,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-25,07%</t>
+          <t>-31,24%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 34,13</t>
+          <t>-5,58; 32,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,25; 39,92</t>
+          <t>-1,82; 38,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-42,7; -14,14</t>
+          <t>-36,28; -4,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,63; -5,45</t>
+          <t>-28,33; -5,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 11,1</t>
+          <t>-16,6; 9,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-44,34; 32,75</t>
+          <t>-46,51; -27,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,0; 4,48</t>
+          <t>-16,8; 6,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 15,01</t>
+          <t>-6,91; 16,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-39,91; 14,58</t>
+          <t>-39,18; -22,66</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-5,95</t>
+          <t>-3,75</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-11,15</t>
+          <t>-10,96</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-8,54</t>
+          <t>-7,38</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,64; 14,75</t>
+          <t>10,5; 14,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13,32; 17,71</t>
+          <t>13,03; 17,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,08; -3,95</t>
+          <t>-5,71; -1,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,56; 6,01</t>
+          <t>1,62; 6,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,45; 10,23</t>
+          <t>5,67; 10,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,3; -5,85</t>
+          <t>-12,89; -9,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,5; 9,7</t>
+          <t>6,64; 9,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10,18; 13,31</t>
+          <t>9,96; 13,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-10,79; -5,63</t>
+          <t>-8,89; -5,98</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-32,9%</t>
+          <t>-20,76%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-40,07%</t>
+          <t>-39,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-37,1%</t>
+          <t>-32,07%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>55,83; 85,44</t>
+          <t>54,05; 86,69</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>70,34; 103,99</t>
+          <t>68,16; 103,49</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-49,51; -23,2</t>
+          <t>-30,19; -11,31</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5,5; 22,88</t>
+          <t>5,37; 22,54</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>18,72; 38,62</t>
+          <t>19,59; 37,85</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-50,14; -21,34</t>
+          <t>-44,76; -33,65</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,29; 43,99</t>
+          <t>27,52; 42,98</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>42,53; 60,45</t>
+          <t>41,99; 58,88</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-45,3; -24,3</t>
+          <t>-37,09; -26,92</t>
         </is>
       </c>
     </row>
